--- a/data/trans_orig/P25C$parches_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según método de dejar de fumar (multirrespuesta) en 2023</t>
+          <t>Población según método de dejar de fumar (multirrespuesta) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3720</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>377</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1629</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1769</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,62 +1104,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97868</t>
+          <t>98657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110241</t>
+          <t>110602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45125</t>
+          <t>45249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145112</t>
+          <t>144762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157808</t>
+          <t>158400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,62 +1330,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>11638</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>3153</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>10838</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,62 +1786,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1771</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7120</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1864,97 +1864,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1156</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3987</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1156</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1156</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>350936</t>
+          <t>352058</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>395914</t>
+          <t>395796</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70861</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79047</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>430716</t>
+          <t>428688</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>476518</t>
+          <t>476199</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>20424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>758</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2546,97 +2546,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1624</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,77 +2679,77 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2496</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>6733</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>3,11%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4499</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>2496</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>7146</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113678</t>
+          <t>114459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129803</t>
+          <t>129692</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62063</t>
+          <t>62290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70820</t>
+          <t>70954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180532</t>
+          <t>181388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198378</t>
+          <t>198437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,82 +2900,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>5984</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2515</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>11341</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4380</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2598</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>11827</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22092</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,62 +3376,62 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2818</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>162533</t>
+          <t>163604</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>180632</t>
+          <t>181527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>105628</t>
+          <t>106890</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>118616</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>275860</t>
+          <t>275752</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296693</t>
+          <t>296451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>26617</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>753362</t>
+          <t>753183</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>824064</t>
+          <t>824349</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>294702</t>
+          <t>294116</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>311951</t>
+          <t>311532</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1058013</t>
+          <t>1056936</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1138617</t>
+          <t>1136007</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C$parches_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>565</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>113074</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98657</t>
+          <t>103717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110602</t>
+          <t>118047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>47658</t>
+          <t>51342</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45249</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>52485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>153446</t>
+          <t>164415</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144762</t>
+          <t>155968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158400</t>
+          <t>169718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>561</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>383048</t>
+          <t>154894</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>352058</t>
+          <t>145442</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>395796</t>
+          <t>161696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76071</t>
+          <t>82421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>77465</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>86193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>459119</t>
+          <t>237315</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428688</t>
+          <t>227159</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>476199</t>
+          <t>245428</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10126</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>971</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>122997</t>
+          <t>142603</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114459</t>
+          <t>133446</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129692</t>
+          <t>151122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>75439</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62290</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70954</t>
+          <t>79542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>190417</t>
+          <t>218043</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181388</t>
+          <t>207945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198437</t>
+          <t>226821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,27 +3145,27 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>174205</t>
+          <t>180084</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>163604</t>
+          <t>169095</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>181527</t>
+          <t>187608</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>113045</t>
+          <t>120999</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106890</t>
+          <t>114165</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118616</t>
+          <t>126834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>287249</t>
+          <t>301083</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>275752</t>
+          <t>289758</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296451</t>
+          <t>311271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4131,67 +4131,67 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1844</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,22 +4201,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,27 +4279,27 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>786038</t>
+          <t>590654</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>753183</t>
+          <t>571253</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>824349</t>
+          <t>605462</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>330202</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>294116</t>
+          <t>320890</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>311532</t>
+          <t>339402</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1090232</t>
+          <t>920856</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1056936</t>
+          <t>901378</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1136007</t>
+          <t>938614</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>27280</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
